--- a/Measurements/27A48 stainless steel L-handle ball lock pin/27A48 inspection report.xlsx
+++ b/Measurements/27A48 stainless steel L-handle ball lock pin/27A48 inspection report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoe\Meng\ManoEng\Measurements\27A48 stainless steel L-handle ball lock pin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE272426-D156-4F76-BDFF-8BB4DA766231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121EFB79-813A-4B5B-AF0E-E9949F51F37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
   </bookViews>
   <sheets>
     <sheet name="FAI" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>Customer</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>Radius</t>
+  </si>
+  <si>
+    <t>VMM</t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -589,18 +592,6 @@
     <xf numFmtId="1" fontId="9" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -613,6 +604,15 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2055,9 +2055,9 @@
       </c>
       <c r="F1" s="34">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
-      </c>
-      <c r="G1" s="36" t="s">
+        <v>46121</v>
+      </c>
+      <c r="G1" s="41" t="s">
         <v>21</v>
       </c>
       <c r="H1" s="17"/>
@@ -2086,7 +2086,7 @@
       <c r="F2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="37"/>
+      <c r="G2" s="42"/>
       <c r="H2" s="17"/>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
@@ -2114,7 +2114,7 @@
       <c r="F3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="38"/>
+      <c r="G3" s="43"/>
       <c r="H3" s="18"/>
       <c r="I3" s="16"/>
       <c r="J3" s="16"/>
@@ -2173,20 +2173,20 @@
       <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="39">
         <v>0.74</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="40">
         <v>0.03</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="40">
         <v>0.03</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="40">
         <f>C5+D5</f>
         <v>0.77</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="40">
         <f>C5-E5</f>
         <v>0.71</v>
       </c>
@@ -2216,20 +2216,20 @@
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="39">
         <v>3.95</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="40">
         <v>0.03</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="40">
         <v>0.03</v>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="40">
         <f>C6+D6</f>
         <v>3.98</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="40">
         <f>C6-E6</f>
         <v>3.9200000000000004</v>
       </c>
@@ -2259,20 +2259,20 @@
       <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="39">
         <v>3.75</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="40">
         <v>0.03</v>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="40">
         <v>0.03</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="40">
         <f t="shared" ref="F7:F11" si="0">C7+D7</f>
         <v>3.78</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="40">
         <f t="shared" ref="G7:G11" si="1">C7-E7</f>
         <v>3.72</v>
       </c>
@@ -2302,29 +2302,41 @@
       <c r="B8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="39">
         <v>0.12</v>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="40">
         <v>0.03</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="40">
         <v>0.03</v>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="40">
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="40">
         <f t="shared" si="1"/>
         <v>0.09</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="3">
+        <v>9.11E-2</v>
+      </c>
+      <c r="J8" s="3">
+        <v>9.2600000000000002E-2</v>
+      </c>
+      <c r="K8" s="3">
+        <v>9.4299999999999995E-2</v>
+      </c>
+      <c r="L8" s="3">
+        <v>9.4700000000000006E-2</v>
+      </c>
+      <c r="M8" s="3">
+        <v>9.4E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
@@ -2393,12 +2405,24 @@
         <f t="shared" si="1"/>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="H10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="K10" s="2">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1.89E-2</v>
+      </c>
+      <c r="M10" s="2">
+        <v>2.1000000000000001E-2</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -2407,29 +2431,41 @@
       <c r="B11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="37">
         <v>45</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="38">
         <v>2</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="38">
         <v>2</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="38">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="38">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
+      <c r="H11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="40">
+        <v>38.83</v>
+      </c>
+      <c r="J11" s="40">
+        <v>38.979999999999997</v>
+      </c>
+      <c r="K11" s="40">
+        <v>38.53</v>
+      </c>
+      <c r="L11" s="40">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="M11" s="40">
+        <v>38.200000000000003</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
@@ -2481,30 +2517,42 @@
       <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="37">
         <v>30</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="38">
         <v>2</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="38">
         <v>2</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="38">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="38">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="40"/>
+      <c r="H13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="40">
+        <v>27.77</v>
+      </c>
+      <c r="J13" s="40">
+        <v>26.6</v>
+      </c>
+      <c r="K13" s="40">
+        <v>26.9</v>
+      </c>
+      <c r="L13" s="40">
+        <v>27.74</v>
+      </c>
+      <c r="M13" s="40">
+        <v>27.98</v>
+      </c>
+      <c r="N13" s="36"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
@@ -2530,12 +2578,24 @@
         <f t="shared" si="3"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="H14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.0199999999999999E-2</v>
+      </c>
+      <c r="J14" s="2">
+        <v>6.3200000000000006E-2</v>
+      </c>
+      <c r="K14" s="2">
+        <v>6.5699999999999995E-2</v>
+      </c>
+      <c r="L14" s="2">
+        <v>6.8599999999999994E-2</v>
+      </c>
+      <c r="M14" s="2">
+        <v>8.0799999999999997E-2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
